--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1609-221-CM26</t>
+          <t>1609-220-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12405.21</v>
+        <v>64452.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1609-220-CM26</t>
+          <t>1609-221-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>64452.54</v>
+        <v>12405.21</v>
       </c>
     </row>
     <row r="20">
@@ -1672,6 +1672,71 @@
       </c>
       <c r="M20" s="2" t="n">
         <v>7083.59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2348-421-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>152784.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/magallanes.xlsx
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
